--- a/output/quarterly_fcst.xlsx
+++ b/output/quarterly_fcst.xlsx
@@ -349,87 +349,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
-        <v>44197</v>
+        <v>44256</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44287</v>
+        <v>44348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44378</v>
+        <v>44440</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44470</v>
+        <v>44531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44562</v>
+        <v>44621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44652</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44743</v>
+        <v>44805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44835</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44927</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45017</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45108</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45200</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45292</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45383</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45474</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45566</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>45658</v>
+        <v>45627</v>
       </c>
     </row>
   </sheetData>
@@ -445,86 +440,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.039201355746544</v>
+        <v>0.0122633135266182</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.00322028065927536</v>
+        <v>0.00910958123043116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0162255563832863</v>
+        <v>0.0133242229140394</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0178842490994885</v>
+        <v>0.0109370807153482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0188361010717453</v>
+        <v>0.0149863103294677</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0138109476927603</v>
+        <v>0.00791493454076129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0051736264827301</v>
+        <v>0.0109271793139065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0107359309493157</v>
+        <v>0.00824063454879287</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00821393807100047</v>
+        <v>0.0111119131259996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0140162595148781</v>
+        <v>0.0104021648315789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.00832044263198439</v>
+        <v>0.00944544701222253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.00628174906696502</v>
+        <v>0.00826647313541323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.0108618278166141</v>
+        <v>0.0000967543965798828</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.00244913370036726</v>
+        <v>0.0135086215817072</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.02044411018464</v>
+        <v>0.00909317734021225</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00467542944969886</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17"/>
+        <v>0.0100008276593782</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -538,86 +530,83 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1"/>
+      <c r="A1" t="n">
+        <v>0.0119831077049675</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0154386076172396</v>
+        <v>0.0141400253425202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.013659691874553</v>
+        <v>0.0175184853447443</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0147210562606515</v>
+        <v>0.0199046809619106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0187902053728565</v>
+        <v>0.0190031356862534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0169553627125188</v>
+        <v>0.0177693024935772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.017702015361575</v>
+        <v>0.0166105273562203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0177996761006313</v>
+        <v>0.0145991900454543</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.011582472105742</v>
+        <v>0.00483560602940246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00778810895998739</v>
+        <v>0.0134257716441824</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0147857088629789</v>
+        <v>0.0154768838642043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0132743582876122</v>
+        <v>-0.0131344227471926</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.00309077541782634</v>
+        <v>0.0123049175497882</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0108434905333412</v>
+        <v>0.0116115724772109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.010683368843575</v>
+        <v>0.00992850569382401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00855271355228642</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.0171450667313933</v>
+        <v>0.0119905577925275</v>
       </c>
     </row>
   </sheetData>
@@ -632,86 +621,83 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1"/>
+      <c r="A1" t="n">
+        <v>0.0142854486517984</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0117326209820302</v>
+        <v>0.0150314772321275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0108960504825199</v>
+        <v>0.0156242751154899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0161802896959579</v>
+        <v>0.00944838653556705</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.018865813994737</v>
+        <v>0.00699843935567633</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0194895834451105</v>
+        <v>0.0162932810153103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0181146635128779</v>
+        <v>0.0158419786947058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0171766330360351</v>
+        <v>0.00650668343248845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0141973969864204</v>
+        <v>-0.0018174553401396</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00865166573210851</v>
+        <v>0.0116869810065715</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0141642234284751</v>
+        <v>0.0148103519240211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.015211729534928</v>
+        <v>-0.00658036484898109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.00936389661164536</v>
+        <v>0.00872296365314064</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.00943938906387804</v>
+        <v>0.0107802660902604</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0106183406935087</v>
+        <v>0.0137436803366078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.00768883773290075</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.0127475748282161</v>
+        <v>0.00939744059426976</v>
       </c>
     </row>
   </sheetData>
@@ -730,82 +716,77 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.00224425051409125</v>
+        <v>0.0151154123346442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0118035666760139</v>
+        <v>0.012424631948694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0133111145982076</v>
+        <v>0.0119942287720807</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0115094421321763</v>
+        <v>0.0148578401410816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.00210185036912208</v>
+        <v>0.0178127339713151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0157817199394054</v>
+        <v>0.0156071313330172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0160173225725187</v>
+        <v>0.0167349508545653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00649367828427385</v>
+        <v>0.0104175961997972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.00656147880518532</v>
+        <v>0.0123851371020795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0120540133077287</v>
+        <v>0.013829324462614</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0139675151322535</v>
+        <v>0.0108500204293118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.00163609476351289</v>
+        <v>0.0102656242615928</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.00368925767125473</v>
+        <v>0.0115218802883047</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00990661223353952</v>
+        <v>0.0106530533734221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0129939038329548</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.0091358992610698</v>
+        <v>0.00974799948317735</v>
       </c>
     </row>
   </sheetData>
@@ -821,87 +802,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -916,55 +892,84 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1"/>
+      <c r="A1" t="n">
+        <v>0.00549866826990097</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2"/>
+      <c r="A2" t="n">
+        <v>0.0341685986820739</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
+      <c r="A3" t="n">
+        <v>0.0174343711356926</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
+      <c r="A4" t="n">
+        <v>0.0450221791175736</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5"/>
+      <c r="A5" t="n">
+        <v>-0.00548268887782655</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6"/>
+      <c r="A6" t="n">
+        <v>0.0172754052916098</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="n">
+        <v>-0.00219755134714994</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8"/>
+      <c r="A8" t="n">
+        <v>0.0185685419762613</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9"/>
+      <c r="A9" t="n">
+        <v>0.0119279231578968</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10"/>
+      <c r="A10" t="n">
+        <v>0.00690327917982181</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="n">
+        <v>-0.00123867417815759</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12"/>
+      <c r="A12" t="n">
+        <v>-0.0579531718404844</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13"/>
+      <c r="A13" t="n">
+        <v>0.0359789609744965</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="n">
+        <v>0.00455127966528401</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15"/>
+      <c r="A15" t="n">
+        <v>0.0109048318994454</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16"/>
-    </row>
-    <row r="17">
-      <c r="A17"/>
+      <c r="A16" t="n">
+        <v>0.00284828658775815</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
